--- a/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-30T07:49:31+00:00</t>
+    <t>2024-04-30T07:52:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-30T07:52:42+00:00</t>
+    <t>2024-04-30T08:03:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-30T08:03:04+00:00</t>
+    <t>2024-04-30T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
+++ b/nr-change-dep/ig/StructureDefinition-mesures-number-of-days.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-30T08:03:54+00:00</t>
+    <t>2024-04-30T08:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
